--- a/Railway_Stations_in_Kolkata.xlsx
+++ b/Railway_Stations_in_Kolkata.xlsx
@@ -7310,7 +7310,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>POINT (88.4012962 22.5800666)</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
@@ -7365,7 +7369,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>POINT (88.4030891 22.5731115)</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -7420,7 +7428,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>POINT (88.3902408 22.5721268)</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
@@ -7475,7 +7487,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>POINT (88.3979434137274 22.472055599999997)</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
